--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260915.xlsx
@@ -6142,10 +6142,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5.963</v>
+        <v>6.1481</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>-5.963</v>
+        <v>-6.1481</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr"/>
       <c r="C20" s="7" t="n">
-        <v>6271</v>
+        <v>6272</v>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="7" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>見込交付割合5.963％（第9期公表値からの逆算）</t>
+          <t>見込交付割合6.148％（第9期公表値からの逆算。基数は標準給付費見込額のみ）</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
